--- a/chore/init-metadonnees-ig/ig/ValueSet-ModifiedAdministrativeGender.xlsx
+++ b/chore/init-metadonnees-ig/ig/ValueSet-ModifiedAdministrativeGender.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:04:08+00:00</t>
+    <t>2026-07-01T08:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
